--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80139</v>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100812</v>
+        <v>100817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>105699</v>
+        <v>105704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>82897</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,9 +2482,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>82897</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,19 +2589,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B5" t="n">
-        <v>91519</v>
+        <v>96778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R5" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,19 +1059,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,57 +1076,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B6" t="n">
-        <v>96775</v>
+        <v>91522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R6" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1156,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         <v>129090304</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129096202</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100817</v>
+        <v>100820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129096200</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129100207</v>
       </c>
       <c r="B12" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R13" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,42 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R14" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,24 +1972,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,57 +1989,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B15" t="n">
-        <v>80174</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,9 +2074,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B16" t="n">
-        <v>56904</v>
+        <v>105707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B17" t="n">
-        <v>105704</v>
+        <v>56904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,7 +2320,7 @@
         <v>129100208</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B19" t="n">
-        <v>82897</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,19 +2482,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>82898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,37 +2522,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2589,9 +2579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,44 +2606,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>80167</v>
+        <v>82898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R21" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>82897</v>
+        <v>80168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R22" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80140</v>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>96778</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R5" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1059,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,57 +1086,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>91522</v>
+        <v>96778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R6" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,19 +1166,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2118,32 +2118,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>105707</v>
+        <v>56904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R16" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>56904</v>
+        <v>105707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R17" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>82898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,9 +2482,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>82898</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,19 +2589,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
         <v>80140</v>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>100820</v>
+        <v>96778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R9" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>96778</v>
+        <v>100820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1807,27 +1807,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R13" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,39 +1892,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R14" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,12 +1989,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2618,32 +2618,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B21" t="n">
-        <v>82898</v>
+        <v>80168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R21" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B22" t="n">
-        <v>80168</v>
+        <v>82898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R22" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80140</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,19 +872,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B4" t="n">
         <v>80140</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +785,7 @@
         <v>129090624</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>96788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R5" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,19 +1059,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,57 +1076,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B6" t="n">
-        <v>96778</v>
+        <v>91529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R6" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1156,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         <v>129090304</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129096202</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>100820</v>
+        <v>100830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129096200</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129100207</v>
       </c>
       <c r="B12" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>129096199</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129100216</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>129091064</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>129100208</v>
       </c>
       <c r="B18" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2618,32 +2618,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>80168</v>
+        <v>82902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R21" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>82898</v>
+        <v>80172</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R22" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         <v>129090251</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>96788</v>
+        <v>100830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R9" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>100830</v>
+        <v>96788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R10" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B19" t="n">
-        <v>82902</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,19 +2482,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>82902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,37 +2522,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2589,9 +2579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090282</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570784</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129100219</v>
       </c>
       <c r="B5" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>129090976</v>
       </c>
       <c r="B6" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100830</v>
+        <v>100837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>80179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R13" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,39 +1892,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>80179</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R14" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,12 +1989,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2118,32 +2118,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B16" t="n">
-        <v>56906</v>
+        <v>105724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B17" t="n">
-        <v>105717</v>
+        <v>56906</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>82871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,9 +2482,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>82902</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,19 +2589,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,44 +2606,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B21" t="n">
-        <v>82902</v>
+        <v>80172</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R21" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B22" t="n">
-        <v>80172</v>
+        <v>82871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R22" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129100219</v>
       </c>
       <c r="B5" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>129090976</v>
       </c>
       <c r="B6" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>129090304</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129096202</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>100837</v>
+        <v>96797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R9" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>96795</v>
+        <v>100839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
         <v>129096200</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129100207</v>
       </c>
       <c r="B12" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,45 +1807,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B13" t="n">
-        <v>80179</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R13" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,9 +1880,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,12 +1912,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1907,7 +1927,7 @@
         <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,50 +2021,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129091064</v>
+        <v>129100216</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570788</v>
+        <v>570768</v>
       </c>
       <c r="R15" t="n">
-        <v>7057793</v>
+        <v>7057817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,24 +2089,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>105724</v>
+        <v>56908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R16" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>56906</v>
+        <v>105726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R17" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,7 +2320,7 @@
         <v>129100208</v>
       </c>
       <c r="B18" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>129100205</v>
       </c>
       <c r="B21" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129100215</v>
       </c>
       <c r="B22" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>129090251</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
         <v>80146</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -991,45 +991,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>96797</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R5" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1059,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,57 +1086,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>96797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R6" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,19 +1166,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,42 +1818,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R13" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1880,24 +1875,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129096199</v>
+        <v>129091064</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,37 +1915,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570785</v>
+        <v>570788</v>
       </c>
       <c r="R14" t="n">
-        <v>7057825</v>
+        <v>7057793</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1977,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,12 +2009,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>96797</v>
+        <v>100839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R9" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>100839</v>
+        <v>96797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R10" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B19" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,19 +2482,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>82873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,37 +2522,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2589,9 +2579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,44 +2606,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>80174</v>
+        <v>82873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R21" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>82873</v>
+        <v>80174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R22" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>96823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R9" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>96797</v>
+        <v>100865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2118,32 +2118,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B16" t="n">
-        <v>56908</v>
+        <v>105752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B17" t="n">
-        <v>105726</v>
+        <v>56908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>82873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,9 +2482,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,19 +2589,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,44 +2606,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B21" t="n">
-        <v>82873</v>
+        <v>80174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R21" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B22" t="n">
-        <v>80174</v>
+        <v>82873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R22" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>96823</v>
+        <v>100867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R9" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>100865</v>
+        <v>96824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R10" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1807,27 +1807,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R13" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,42 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R14" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,24 +1972,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,57 +1989,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,9 +2074,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>105752</v>
+        <v>56908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R16" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>56908</v>
+        <v>105754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R17" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100867</v>
+        <v>100868</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1807,45 +1807,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R13" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,9 +1880,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,12 +1912,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2001,50 +2021,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129091064</v>
+        <v>129100216</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570788</v>
+        <v>570768</v>
       </c>
       <c r="R15" t="n">
-        <v>7057793</v>
+        <v>7057817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,24 +2089,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B16" t="n">
-        <v>56908</v>
+        <v>105755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B17" t="n">
-        <v>105754</v>
+        <v>56908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2618,32 +2618,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>80174</v>
+        <v>82873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R21" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>82873</v>
+        <v>80174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R22" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>96829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R5" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,19 +1059,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,57 +1076,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B6" t="n">
-        <v>96825</v>
+        <v>91539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R6" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1156,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         <v>129090304</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129096202</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100868</v>
+        <v>100872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96825</v>
+        <v>96829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129096200</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129100207</v>
       </c>
       <c r="B12" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,27 +1924,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>80183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R14" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>105755</v>
+        <v>56908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R16" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>56908</v>
+        <v>105759</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R17" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,7 +2320,7 @@
         <v>129100208</v>
       </c>
       <c r="B18" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -991,45 +991,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>96829</v>
+        <v>91539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R5" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1059,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,57 +1086,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>91539</v>
+        <v>96829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R6" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,19 +1166,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>100872</v>
+        <v>96829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R9" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>96829</v>
+        <v>100872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1924,27 +1924,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>80183</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R14" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>80183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R15" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +785,7 @@
         <v>129090282</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>129090304</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>129096202</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>100872</v>
+        <v>100874</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129096200</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129100207</v>
       </c>
       <c r="B12" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,50 +1807,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129091064</v>
+        <v>129100216</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570788</v>
+        <v>570768</v>
       </c>
       <c r="R13" t="n">
-        <v>7057793</v>
+        <v>7057817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,24 +1875,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129096199</v>
+        <v>129091064</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,37 +1915,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570785</v>
+        <v>570788</v>
       </c>
       <c r="R14" t="n">
-        <v>7057825</v>
+        <v>7057793</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1977,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B15" t="n">
-        <v>80183</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B16" t="n">
-        <v>56908</v>
+        <v>105761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B17" t="n">
-        <v>105759</v>
+        <v>56908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,7 +2320,7 @@
         <v>129100208</v>
       </c>
       <c r="B18" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
         <v>80149</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80149</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96831</v>
+        <v>96835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>96831</v>
+        <v>100878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R9" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>100874</v>
+        <v>96835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R10" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,42 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R14" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,24 +1972,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129096199</v>
+        <v>129091064</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,37 +2012,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570785</v>
+        <v>570788</v>
       </c>
       <c r="R15" t="n">
-        <v>7057825</v>
+        <v>7057793</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,9 +2074,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>105761</v>
+        <v>56908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R16" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>56908</v>
+        <v>105765</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R17" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2618,32 +2618,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B21" t="n">
-        <v>82878</v>
+        <v>80177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R21" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B22" t="n">
-        <v>80177</v>
+        <v>82878</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R22" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
         <v>80149</v>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100878</v>
+        <v>100886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96835</v>
+        <v>96843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1807,45 +1807,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B13" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R13" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,9 +1880,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,12 +1912,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2001,50 +2021,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129091064</v>
+        <v>129100216</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570788</v>
+        <v>570768</v>
       </c>
       <c r="R15" t="n">
-        <v>7057793</v>
+        <v>7057817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,24 +2089,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
         <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>105765</v>
+        <v>105775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2618,32 +2618,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>80177</v>
+        <v>82878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R21" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>82878</v>
+        <v>80177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R22" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1924,27 +1924,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R14" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,19 +2482,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,37 +2522,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2589,9 +2579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,42 +1818,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R13" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1880,24 +1875,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,57 +1892,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B14" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R14" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,9 +1977,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R15" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2618,32 +2618,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B21" t="n">
-        <v>82878</v>
+        <v>80177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R21" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B22" t="n">
-        <v>80177</v>
+        <v>82878</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R22" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B5" t="n">
-        <v>91546</v>
+        <v>96846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R5" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,19 +1059,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,57 +1076,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B6" t="n">
-        <v>96843</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R6" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1156,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1402,7 +1402,7 @@
         <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>100886</v>
+        <v>100889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>96843</v>
+        <v>96846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2118,32 +2118,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B16" t="n">
-        <v>56908</v>
+        <v>105778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B17" t="n">
-        <v>105775</v>
+        <v>56908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,9 +2482,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,19 +2589,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100198</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570782</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129100219</v>
+        <v>129090976</v>
       </c>
       <c r="B5" t="n">
-        <v>96846</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570772</v>
+        <v>570763</v>
       </c>
       <c r="R5" t="n">
-        <v>7057892</v>
+        <v>7057867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1059,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,57 +1086,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129090976</v>
+        <v>129100219</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>96846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570763</v>
+        <v>570772</v>
       </c>
       <c r="R6" t="n">
-        <v>7057867</v>
+        <v>7057892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,19 +1166,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129096199</v>
+        <v>129091064</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,37 +1818,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570785</v>
+        <v>570788</v>
       </c>
       <c r="R13" t="n">
-        <v>7057825</v>
+        <v>7057793</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,9 +1880,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,62 +1912,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129091064</v>
+        <v>129100216</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570788</v>
+        <v>570768</v>
       </c>
       <c r="R14" t="n">
-        <v>7057793</v>
+        <v>7057817</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,24 +1992,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129096199</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570785</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,44 +2106,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096191</v>
+        <v>129096195</v>
       </c>
       <c r="B16" t="n">
-        <v>105778</v>
+        <v>56908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570777</v>
+        <v>570768</v>
       </c>
       <c r="R16" t="n">
-        <v>7057880</v>
+        <v>7057887</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,32 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096195</v>
+        <v>129096191</v>
       </c>
       <c r="B17" t="n">
-        <v>56908</v>
+        <v>105778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570768</v>
+        <v>570777</v>
       </c>
       <c r="R17" t="n">
-        <v>7057887</v>
+        <v>7057880</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,19 +2482,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,37 +2522,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2589,9 +2579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,44 +2606,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100205</v>
+        <v>129100215</v>
       </c>
       <c r="B21" t="n">
-        <v>80177</v>
+        <v>82878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570776</v>
+        <v>570770</v>
       </c>
       <c r="R21" t="n">
-        <v>7057882</v>
+        <v>7057885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,32 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100215</v>
+        <v>129100205</v>
       </c>
       <c r="B22" t="n">
-        <v>82878</v>
+        <v>80177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570770</v>
+        <v>570776</v>
       </c>
       <c r="R22" t="n">
-        <v>7057885</v>
+        <v>7057882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B9" t="n">
-        <v>100889</v>
+        <v>96846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R9" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B10" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,42 +1818,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R13" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1880,24 +1875,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,57 +1892,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B14" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R14" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,9 +1977,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,39 +2009,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R15" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B2" t="n">
         <v>80149</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R2" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090624</v>
       </c>
       <c r="B3" t="n">
         <v>80149</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570765</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,9 +2482,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B20" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,37 +2532,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,19 +2589,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129090282</v>
+        <v>129100198</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570784</v>
+        <v>570782</v>
       </c>
       <c r="R2" t="n">
-        <v>7057839</v>
+        <v>7057865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090624</v>
+        <v>129090282</v>
       </c>
       <c r="B3" t="n">
         <v>80149</v>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570765</v>
+        <v>570784</v>
       </c>
       <c r="R3" t="n">
-        <v>7057891</v>
+        <v>7057839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129100198</v>
+        <v>129090624</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570782</v>
+        <v>570765</v>
       </c>
       <c r="R4" t="n">
-        <v>7057865</v>
+        <v>7057891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,14 +952,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090470</v>
+        <v>129090899</v>
       </c>
       <c r="B9" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570781</v>
+        <v>570778</v>
       </c>
       <c r="R9" t="n">
-        <v>7057902</v>
+        <v>7057898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090899</v>
+        <v>129090470</v>
       </c>
       <c r="B10" t="n">
-        <v>100889</v>
+        <v>96846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570778</v>
+        <v>570781</v>
       </c>
       <c r="R10" t="n">
-        <v>7057898</v>
+        <v>7057902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,12 +1601,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1807,27 +1807,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129096199</v>
+        <v>129100216</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570785</v>
+        <v>570768</v>
       </c>
       <c r="R13" t="n">
-        <v>7057825</v>
+        <v>7057817</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129091064</v>
+        <v>129096199</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,42 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570788</v>
+        <v>570785</v>
       </c>
       <c r="R14" t="n">
-        <v>7057793</v>
+        <v>7057825</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,24 +1972,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,57 +1989,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129100216</v>
+        <v>129091064</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570768</v>
+        <v>570788</v>
       </c>
       <c r="R15" t="n">
-        <v>7057817</v>
+        <v>7057793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,9 +2074,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,12 +2106,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129090603</v>
+        <v>129096201</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570757</v>
+        <v>570811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057886</v>
+        <v>7057913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2482,19 +2482,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129096201</v>
+        <v>129090603</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,37 +2522,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570811</v>
+        <v>570757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057913</v>
+        <v>7057886</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2589,9 +2579,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,12 +2606,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100198</v>
+        <v>129090976</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570782</v>
+        <v>570763</v>
       </c>
       <c r="R2" t="n">
-        <v>7057865</v>
+        <v>7057867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +743,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129090282</v>
+        <v>129090603</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570784</v>
+        <v>570757</v>
       </c>
       <c r="R3" t="n">
-        <v>7057839</v>
+        <v>7057886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129090624</v>
+        <v>129100215</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570765</v>
+        <v>570770</v>
       </c>
       <c r="R4" t="n">
-        <v>7057891</v>
+        <v>7057885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +957,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129090976</v>
+        <v>129090762</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>101298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570763</v>
+        <v>570751</v>
       </c>
       <c r="R5" t="n">
-        <v>7057867</v>
+        <v>7057897</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129100219</v>
+        <v>129090899</v>
       </c>
       <c r="B6" t="n">
-        <v>96846</v>
+        <v>101298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570772</v>
+        <v>570778</v>
       </c>
       <c r="R6" t="n">
-        <v>7057892</v>
+        <v>7057898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1161,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,44 +1188,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129090304</v>
+        <v>129090470</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570801</v>
+        <v>570781</v>
       </c>
       <c r="R7" t="n">
-        <v>7057842</v>
+        <v>7057902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1275,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129096202</v>
+        <v>129100219</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570759</v>
+        <v>570772</v>
       </c>
       <c r="R8" t="n">
-        <v>7057838</v>
+        <v>7057892</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,44 +1392,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129090899</v>
+        <v>129090304</v>
       </c>
       <c r="B9" t="n">
-        <v>100889</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570778</v>
+        <v>570801</v>
       </c>
       <c r="R9" t="n">
-        <v>7057898</v>
+        <v>7057842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1479,7 +1484,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,44 +1499,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129090470</v>
+        <v>129090665</v>
       </c>
       <c r="B10" t="n">
-        <v>96846</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570781</v>
+        <v>570744</v>
       </c>
       <c r="R10" t="n">
-        <v>7057902</v>
+        <v>7057883</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1591,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,26 +1606,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129096200</v>
+        <v>129096199</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570789</v>
+        <v>570785</v>
       </c>
       <c r="R11" t="n">
-        <v>7057871</v>
+        <v>7057825</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,32 +1715,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129100207</v>
+        <v>129096200</v>
       </c>
       <c r="B12" t="n">
-        <v>80177</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570777</v>
+        <v>570789</v>
       </c>
       <c r="R12" t="n">
-        <v>7057825</v>
+        <v>7057871</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,39 +1800,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129100216</v>
+        <v>129096201</v>
       </c>
       <c r="B13" t="n">
-        <v>80184</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1842,13 +1847,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570768</v>
+        <v>570811</v>
       </c>
       <c r="R13" t="n">
-        <v>7057817</v>
+        <v>7057913</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,26 +1897,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129096199</v>
+        <v>129096202</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570785</v>
+        <v>570759</v>
       </c>
       <c r="R14" t="n">
-        <v>7057825</v>
+        <v>7057838</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129091064</v>
+        <v>129090282</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,39 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570788</v>
+        <v>570784</v>
       </c>
       <c r="R15" t="n">
-        <v>7057793</v>
+        <v>7057839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2086,12 +2086,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129096195</v>
+        <v>129090624</v>
       </c>
       <c r="B16" t="n">
-        <v>56908</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,37 +2124,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570768</v>
+        <v>570765</v>
       </c>
       <c r="R16" t="n">
-        <v>7057887</v>
+        <v>7057891</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2186,14 +2181,19 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sång</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,22 +2208,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129096191</v>
+        <v>129100205</v>
       </c>
       <c r="B17" t="n">
-        <v>105778</v>
+        <v>80460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570777</v>
+        <v>570776</v>
       </c>
       <c r="R17" t="n">
-        <v>7057880</v>
+        <v>7057882</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2305,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129100208</v>
+        <v>129100207</v>
       </c>
       <c r="B18" t="n">
-        <v>80185</v>
+        <v>80460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570771</v>
+        <v>570777</v>
       </c>
       <c r="R18" t="n">
-        <v>7057817</v>
+        <v>7057825</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,27 +2414,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129096201</v>
+        <v>129100216</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570811</v>
+        <v>570768</v>
       </c>
       <c r="R19" t="n">
-        <v>7057913</v>
+        <v>7057817</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,57 +2499,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129090603</v>
+        <v>129100208</v>
       </c>
       <c r="B20" t="n">
-        <v>82878</v>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570757</v>
+        <v>570771</v>
       </c>
       <c r="R20" t="n">
-        <v>7057886</v>
+        <v>7057817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2579,19 +2579,9 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2606,22 +2596,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129100215</v>
+        <v>129090251</v>
       </c>
       <c r="B21" t="n">
-        <v>82878</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,34 +2619,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570770</v>
+        <v>570755</v>
       </c>
       <c r="R21" t="n">
-        <v>7057885</v>
+        <v>7057843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2686,9 +2681,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,57 +2713,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129100205</v>
+        <v>129091064</v>
       </c>
       <c r="B22" t="n">
-        <v>80177</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramariset, Ång</t>
+          <t>Käringnålmyran, Käringnålmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570776</v>
+        <v>570788</v>
       </c>
       <c r="R22" t="n">
-        <v>7057882</v>
+        <v>7057793</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2783,9 +2798,24 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2800,22 +2830,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129090251</v>
+        <v>129100198</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,21 +2871,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käringnålmyran, Käringnålmyran, Ång</t>
+          <t>Ramariset, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570755</v>
+        <v>570782</v>
       </c>
       <c r="R23" t="n">
-        <v>7057843</v>
+        <v>7057865</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2885,24 +2910,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2917,15 +2932,214 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129096195</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ramariset, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570768</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7057887</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129096191</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ramariset, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570777</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7057880</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49704-2025 artfynd.xlsx
+++ b/artfynd/A 49704-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090976</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090603</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100215</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090762</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100219</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090304</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090665</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096199</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096200</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096201</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096202</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090282</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090624</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100205</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100207</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100216</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100208</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090251</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091064</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100198</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3043,6 +3158,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096195</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3140,8 +3260,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129096191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>